--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,12 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -23193,7 +23211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23237,6 +23255,120 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1974_75_0378 'MKZ Rájec – Jestřebí' prev→CLUB_S1973_74_0458 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0013</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0013 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1974_75_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0021</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0021 'Kvalifikace o II.ČNHL' (L35, parent=NODE_S1974_75_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0026 'KVAL Kvalifikace o divizi' (L45, parent=NODE_S1974_75_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0027</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0027 'KVAL Slovensko' (L45, parent=NODE_S1974_75_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0129</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0129 'Kvalifikace o 2. ČNHL sk. A' (L35, parent=NODE_S1974_75_0021) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0130</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0130 'Kvalifikace o 2. ČNHL sk. B' (L35, parent=NODE_S1974_75_0021) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -28090,21 +28222,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -36794,7 +36911,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
@@ -37346,7 +37462,6 @@
         </is>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -40311,7 +40426,6 @@
         </is>
       </c>
     </row>
-    <row r="196"/>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
@@ -42755,7 +42869,6 @@
         </is>
       </c>
     </row>
-    <row r="251"/>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
@@ -43008,7 +43121,6 @@
         </is>
       </c>
     </row>
-    <row r="258"/>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
@@ -44569,7 +44681,6 @@
         </is>
       </c>
     </row>
-    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -48097,7 +48208,6 @@
         </is>
       </c>
     </row>
-    <row r="376"/>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
@@ -50772,7 +50882,6 @@
         </is>
       </c>
     </row>
-    <row r="439"/>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
@@ -52854,7 +52963,6 @@
         </is>
       </c>
     </row>
-    <row r="488"/>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
@@ -54093,6 +54201,215 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0378</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0378 'MKZ Rájec – Jestřebí' prev→CLUB_S1973_74_0458 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0013</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1974_75_0013 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1974_75_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0021</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1974_75_0021 'Kvalifikace o II.ČNHL' (L35, parent=NODE_S1974_75_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0026</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1974_75_0026 'KVAL Kvalifikace o divizi' (L45, parent=NODE_S1974_75_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0027</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1974_75_0027 'KVAL Slovensko' (L45, parent=NODE_S1974_75_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0129</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1974_75_0129 'Kvalifikace o 2. ČNHL sk. A' (L35, parent=NODE_S1974_75_0021) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0130</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1974_75_0130 'Kvalifikace o 2. ČNHL sk. B' (L35, parent=NODE_S1974_75_0021) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23211,7 +23211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23261,7 +23261,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1974_75_0378 'MKZ Rájec – Jestřebí' prev→CLUB_S1973_74_0458 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -23271,14 +23271,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1974_75_0013</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0013 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1974_75_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23288,14 +23283,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1974_75_0021</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0021 'Kvalifikace o II.ČNHL' (L35, parent=NODE_S1974_75_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23305,14 +23295,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1974_75_0026</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0026 'KVAL Kvalifikace o divizi' (L45, parent=NODE_S1974_75_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23322,14 +23307,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1974_75_0027</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0027 'KVAL Slovensko' (L45, parent=NODE_S1974_75_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23339,14 +23319,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1974_75_0129</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0129 'Kvalifikace o 2. ČNHL sk. A' (L35, parent=NODE_S1974_75_0021) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23356,17 +23331,480 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S1974_75_0130</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1974_75_0130 'Kvalifikace o 2. ČNHL sk. B' (L35, parent=NODE_S1974_75_0021) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -28222,6 +28660,21 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -32079,7 +32532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J513"/>
+  <dimension ref="A1:J521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -32422,12 +32875,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -32763,12 +33216,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -32805,12 +33258,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -33450,12 +33903,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -33581,12 +34034,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -33838,12 +34291,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34095,12 +34548,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -34137,12 +34590,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -34268,12 +34721,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou. || TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Kaučuk Kralupy</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -34352,12 +34805,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34525,12 +34978,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -34787,12 +35240,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -34871,12 +35324,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -34960,12 +35413,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -35484,12 +35937,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -35820,12 +36273,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -35904,12 +36357,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -36764,12 +37217,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Vyšné Opátske = TJ Pokrok Vyšné Opátske (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj (okres Sabinov). 'Opátske' bez diakritiky. NE Vysné Opátske mestska cast Kosic! city Vyšné Opátske.</t>
+          <t>Vyšné Opátske = TJ Pokrok Vyšné Opátske (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj (okres Sabinov). 'Opátske' bez diakritiky. NE Vysné Opátske mestska cast Kosic! city Vyšné Opátske. || TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Pokrok Vyšné Opátske</t>
+          <t>Vyšné Opátske</t>
         </is>
       </c>
     </row>
@@ -36843,12 +37296,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické Služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické Služby** = mestske technicke sluzby (cisteni, sbery odpadu). city Děčín.</t>
+          <t>Děčín = TJ Technické Služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické Služby** = mestske technicke sluzby (cisteni, sbery odpadu). city Děčín. || TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Technické Služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -36911,6 +37364,7 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
@@ -37462,6 +37916,7 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -40426,6 +40881,7 @@
         </is>
       </c>
     </row>
+    <row r="196"/>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
@@ -40548,12 +41004,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -41151,12 +41607,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -42869,6 +43325,7 @@
         </is>
       </c>
     </row>
+    <row r="251"/>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
@@ -43121,6 +43578,7 @@
         </is>
       </c>
     </row>
+    <row r="258"/>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
@@ -44681,6 +45139,7 @@
         </is>
       </c>
     </row>
+    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -45302,12 +45761,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -46456,12 +46915,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -46770,12 +47229,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -48208,6 +48667,7 @@
         </is>
       </c>
     </row>
+    <row r="376"/>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
@@ -49180,12 +49640,12 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -50072,12 +50532,12 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -50240,12 +50700,12 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>Bystřice</t>
+          <t>Bystřice pod Hostýnem</t>
         </is>
       </c>
     </row>
@@ -50287,12 +50747,12 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -50882,6 +51342,7 @@
         </is>
       </c>
     </row>
+    <row r="439"/>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
@@ -51004,12 +51465,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -51219,12 +51680,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm. || TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>MEZ Frenštát</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -52963,6 +53424,7 @@
         </is>
       </c>
     </row>
+    <row r="488"/>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
@@ -53080,12 +53542,12 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>Nitra = TJ Slávia VŠP Nitra (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. **VŠP** = Vysoká škola pedagogická (dnes Univerzita Konštantína Filozofa, UKF Nitra). city Nitra.</t>
+          <t>Nitra = TJ Slávia VŠP Nitra (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. **VŠP** = Vysoká škola pedagogická (dnes Univerzita Konštantína Filozofa, UKF Nitra). city Nitra. || TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>Slávia VŠP Nitra</t>
+          <t>VŠP Nitra</t>
         </is>
       </c>
     </row>
@@ -53206,12 +53668,12 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom.</t>
+          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom. || TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>Družstevník Krizovany nad Dudváhom</t>
+          <t>Krizovany nad Dudváhom</t>
         </is>
       </c>
     </row>
@@ -53290,12 +53752,12 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>Bánovce nad Bebravou = TJ Slávia Zornica Bánovce nad Bebravou (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. **Zornica** = obuvnicky podnik (vyrobce obuvi Zornica). city Bánovce nad Bebravou.</t>
+          <t>Bánovce nad Bebravou = TJ Slávia Zornica Bánovce nad Bebravou (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. **Zornica** = obuvnicky podnik (vyrobce obuvi Zornica). city Bánovce nad Bebravou. || TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>Slávia Zornica Bánovce nad Bebravou</t>
+          <t>Bánovce nad Bebravou</t>
         </is>
       </c>
     </row>
@@ -53955,6 +54417,262 @@
       <c r="J513" t="inlineStr">
         <is>
           <t>Velký Šariš</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0128</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0196</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0251</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0258</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0294</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0376</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0439</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0488</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54211,11 +54929,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -54260,21 +54978,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0378</t>
+          <t>CLUB_S1974_75_0007</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0378 'MKZ Rájec – Jestřebí' prev→CLUB_S1973_74_0458 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -54282,21 +54998,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1974_75_0013</t>
+          <t>CLUB_S1974_75_0015</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1974_75_0013 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1974_75_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -54304,21 +55018,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1974_75_0021</t>
+          <t>CLUB_S1974_75_0016</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1974_75_0021 'Kvalifikace o II.ČNHL' (L35, parent=NODE_S1974_75_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -54326,21 +55038,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1974_75_0026</t>
+          <t>CLUB_S1974_75_0031</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1974_75_0026 'KVAL Kvalifikace o divizi' (L45, parent=NODE_S1974_75_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -54348,21 +55058,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1974_75_0027</t>
+          <t>CLUB_S1974_75_0034</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1974_75_0027 'KVAL Slovensko' (L45, parent=NODE_S1974_75_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -54370,21 +55078,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S1974_75_0129</t>
+          <t>CLUB_S1974_75_0040</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1974_75_0129 'Kvalifikace o 2. ČNHL sk. A' (L35, parent=NODE_S1974_75_0021) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -54392,24 +55098,802 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S1974_75_0130</t>
+          <t>CLUB_S1974_75_0046</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1974_75_0130 'Kvalifikace o 2. ČNHL sk. B' (L35, parent=NODE_S1974_75_0021) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0047</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0050</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0052</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0056</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0059</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0062</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0064</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0066</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0078</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0086</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0088</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0108</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0515</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0199</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0213</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0213</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0232</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0309</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0336</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0343</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0378</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0399</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0414</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0420</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0424</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0425</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0442</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0447</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0491</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0494</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0496</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0128</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0196</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0251</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0258</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0294</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0376</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0439</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0488</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23211,7 +23211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23261,7 +23261,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -23273,7 +23273,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23285,7 +23285,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23297,7 +23297,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23309,7 +23309,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23321,7 +23321,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23333,7 +23333,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23345,7 +23345,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23357,7 +23357,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23369,7 +23369,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23381,7 +23381,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -23393,7 +23393,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -23405,7 +23405,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23417,7 +23417,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -23429,7 +23429,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23441,7 +23441,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -23453,7 +23453,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -23465,7 +23465,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -23477,7 +23477,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -23489,7 +23489,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -23501,7 +23501,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -23525,7 +23525,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -23537,7 +23537,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -23549,7 +23549,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -23561,7 +23561,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23573,7 +23573,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -23585,7 +23585,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -23597,7 +23597,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -23609,7 +23609,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -23621,7 +23621,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -23633,7 +23633,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -23645,7 +23645,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -23657,7 +23657,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -23669,142 +23669,10 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -23821,7 +23689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23880,6 +23748,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23922,6 +23795,11 @@
           <t>12 týmů, jeden stůl. Mistr: SONP Kladno. Bez playoff.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23969,6 +23847,11 @@
           <t>Série Zvolen – Ingstav 1:4. 1., 2. a 5. utkání doma; případné 7. v Karviné.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24053,6 +23936,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24095,6 +23983,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24137,6 +24030,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24179,6 +24077,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24221,6 +24124,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24263,6 +24171,11 @@
           <t>II.ČNHL: 3 skupiny po 8. Nově založená soutěž.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24305,6 +24218,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24347,6 +24265,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24389,6 +24312,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24473,6 +24401,11 @@
           <t>Divize: 6 skupin CZ (A-F) + SVK západ/východ + kvalifikace.</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24515,6 +24448,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24557,6 +24495,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24599,6 +24542,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24641,6 +24589,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24683,6 +24636,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24725,6 +24683,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24819,6 +24782,11 @@
           <t>V západoslovenské divizi chybí v křížové tabulce část utkání.</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -24866,6 +24834,11 @@
           <t>Ve východní slovenské divizi chybí část utkání; Detva – Vyšné Opátske je zdrojově nejasné.</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24997,6 +24970,11 @@
           <t>Konflikt zdrojů raw/prepared vs PDF: český blok veden jako kvalifikace o divizi; přímé postupy a regionální série zachyceny poznámkami a SERIES.</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0024</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -25086,6 +25064,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0029</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25212,6 +25195,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0035</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -25254,6 +25242,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0036</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -25296,6 +25289,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0037</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -25338,6 +25336,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0038</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -25380,6 +25383,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0039</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -25548,6 +25556,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -25590,6 +25603,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -25632,6 +25650,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0042</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -25674,6 +25697,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0043</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -25758,6 +25786,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0044</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25800,6 +25833,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0045</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25842,6 +25880,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0046</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25884,6 +25927,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0047</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -25926,6 +25974,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -25968,6 +26021,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0051</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -26010,6 +26068,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0052</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -26225,6 +26288,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0058</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -26267,6 +26335,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0059</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -26309,6 +26382,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0060</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -26351,6 +26429,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0061</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -26393,6 +26476,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0062</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -26477,6 +26565,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0064</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -26519,6 +26612,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0065</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -26561,6 +26659,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0066</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -26608,6 +26711,11 @@
           <t>kvalifikace</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0068</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -26655,6 +26763,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0069</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -26697,6 +26810,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0070</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -26739,6 +26857,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0071</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -26781,6 +26904,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0072</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26823,6 +26951,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0073</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -26865,6 +26998,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0074</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -26907,6 +27045,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0075</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -26996,6 +27139,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0078</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -27594,6 +27742,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0088</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27678,6 +27831,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0090</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27720,6 +27878,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0091</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -27762,6 +27925,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0093</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28150,6 +28318,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0100</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -28192,6 +28365,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0101</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -28276,6 +28454,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0104</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -28318,6 +28501,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0105</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -28360,6 +28548,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0106</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -28449,6 +28642,11 @@
           <t>Kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0108</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -28533,6 +28731,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0116</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -28575,6 +28778,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0117</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -28617,6 +28825,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0118</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -28657,6 +28870,11 @@
       <c r="J113" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>NODE_S1973_74_0119</t>
         </is>
       </c>
     </row>
@@ -32875,12 +33093,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33258,12 +33476,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -34034,12 +34252,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -34548,12 +34766,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -34590,12 +34808,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -36357,12 +36575,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -41607,12 +41825,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -46915,12 +47133,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -47229,12 +47447,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -50700,12 +50918,12 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>Bystřice pod Hostýnem</t>
+          <t>Bystřice u Benešova</t>
         </is>
       </c>
     </row>
@@ -51465,12 +51683,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -54929,7 +55147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -54983,12 +55201,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0007</t>
+          <t>CLUB_S1974_75_0015</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55003,12 +55221,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0015</t>
+          <t>CLUB_S1974_75_0031</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55023,12 +55241,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0016</t>
+          <t>CLUB_S1974_75_0040</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55043,12 +55261,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0031</t>
+          <t>CLUB_S1974_75_0050</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55063,12 +55281,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0034</t>
+          <t>CLUB_S1974_75_0052</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55083,12 +55301,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0040</t>
+          <t>CLUB_S1974_75_0056</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55103,12 +55321,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0046</t>
+          <t>CLUB_S1974_75_0059</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -55123,12 +55341,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0047</t>
+          <t>CLUB_S1974_75_0062</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55143,12 +55361,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0050</t>
+          <t>CLUB_S1974_75_0064</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55163,12 +55381,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0052</t>
+          <t>CLUB_S1974_75_0066</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55183,12 +55401,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0056</t>
+          <t>CLUB_S1974_75_0078</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55203,12 +55421,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0059</t>
+          <t>CLUB_S1974_75_0086</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55223,12 +55441,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0062</t>
+          <t>CLUB_S1974_75_0108</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55243,12 +55461,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0064</t>
+          <t>CLUB_S1974_75_0515</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55263,12 +55481,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0066</t>
+          <t>CLUB_S1974_75_0199</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55283,12 +55501,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0078</t>
+          <t>CLUB_S1974_75_0213</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55303,12 +55521,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0086</t>
+          <t>CLUB_S1974_75_0232</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -55323,12 +55541,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0088</t>
+          <t>CLUB_S1974_75_0309</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55343,12 +55561,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0108</t>
+          <t>CLUB_S1974_75_0378</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55363,12 +55581,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0515</t>
+          <t>CLUB_S1974_75_0399</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55383,12 +55601,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0199</t>
+          <t>CLUB_S1974_75_0414</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -55403,7 +55621,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0213</t>
+          <t>CLUB_S1974_75_0420</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -55423,12 +55641,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0213</t>
+          <t>CLUB_S1974_75_0425</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55443,12 +55661,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0232</t>
+          <t>CLUB_S1974_75_0447</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55463,12 +55681,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0309</t>
+          <t>CLUB_S1974_75_0491</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55483,12 +55701,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0336</t>
+          <t>CLUB_S1974_75_0494</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55503,12 +55721,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0343</t>
+          <t>CLUB_S1974_75_0496</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55523,12 +55741,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0378</t>
+          <t>CLUB_S1974_75_0128</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55543,12 +55761,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0399</t>
+          <t>CLUB_S1974_75_0196</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55563,12 +55781,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0414</t>
+          <t>CLUB_S1974_75_0251</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55583,12 +55801,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0420</t>
+          <t>CLUB_S1974_75_0258</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55603,12 +55821,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0424</t>
+          <t>CLUB_S1974_75_0294</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55623,12 +55841,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0425</t>
+          <t>CLUB_S1974_75_0376</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55643,12 +55861,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0442</t>
+          <t>CLUB_S1974_75_0439</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55663,237 +55881,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1974_75_0447</t>
+          <t>CLUB_S1974_75_0488</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0491</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0494</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0496</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0128</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0196</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0251</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0258</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0294</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0376</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0439</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0488</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -23211,7 +23211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23259,21 +23259,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] Sokol Čimice — odstoupil</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23285,7 +23290,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23297,7 +23302,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23309,7 +23314,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23321,7 +23326,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23333,7 +23338,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23345,7 +23350,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23357,7 +23362,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23369,7 +23374,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23381,7 +23386,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -23393,7 +23398,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -23405,7 +23410,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23417,7 +23422,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -23429,7 +23434,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23441,7 +23446,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -23453,7 +23458,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -23465,7 +23470,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -23477,7 +23482,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -23489,7 +23494,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -23501,7 +23506,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -23513,7 +23518,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -23525,7 +23530,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -23537,7 +23542,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -23549,7 +23554,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -23561,7 +23566,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23573,7 +23578,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -23585,7 +23590,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -23673,6 +23678,18 @@
         </is>
       </c>
       <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -65479,7 +65496,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Pražský krajský přebor / Sokol Čimice — odstoupil</t>
+          <t>Pražský krajský přebor</t>
         </is>
       </c>
       <c r="C10" s="2" t="n"/>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -37599,7 +37599,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
@@ -38151,7 +38150,6 @@
         </is>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -41116,7 +41114,6 @@
         </is>
       </c>
     </row>
-    <row r="196"/>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
@@ -43560,7 +43557,6 @@
         </is>
       </c>
     </row>
-    <row r="251"/>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
@@ -43813,7 +43809,6 @@
         </is>
       </c>
     </row>
-    <row r="258"/>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
@@ -45374,7 +45369,6 @@
         </is>
       </c>
     </row>
-    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -48902,7 +48896,6 @@
         </is>
       </c>
     </row>
-    <row r="376"/>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
@@ -51577,7 +51570,6 @@
         </is>
       </c>
     </row>
-    <row r="439"/>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
@@ -53659,7 +53651,6 @@
         </is>
       </c>
     </row>
-    <row r="488"/>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -23706,7 +23706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23770,6 +23770,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28895,21 +28905,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -24047,6 +24047,16 @@
           <t>NODE_S1974_75_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24061,6 +24071,14 @@
         <is>
           <t>NODE_S1973_74_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -24094,6 +24112,8 @@
           <t>NODE_S1974_75_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24108,6 +24128,14 @@
         <is>
           <t>NODE_S1973_74_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -24141,6 +24169,8 @@
           <t>NODE_S1974_75_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24155,6 +24185,14 @@
         <is>
           <t>NODE_S1973_74_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -24898,6 +24936,8 @@
           <t>NODE_S1974_75_0014</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24907,6 +24947,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -24940,6 +24988,8 @@
           <t>NODE_S1974_75_0014</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24949,6 +24999,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -25306,6 +25364,8 @@
           <t>NODE_S1974_75_0030</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25320,6 +25380,14 @@
         <is>
           <t>NODE_S1973_74_0037</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -25531,6 +25599,8 @@
           <t>NODE_S1974_75_0034</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25540,6 +25610,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -25761,6 +25839,8 @@
           <t>NODE_S1974_75_0034</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25770,6 +25850,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -26493,6 +26581,8 @@
           <t>NODE_S1974_75_0055</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26507,6 +26597,14 @@
         <is>
           <t>NODE_S1973_74_0062</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -27413,6 +27511,8 @@
           <t>NODE_S1974_75_0073</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27422,6 +27522,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -27942,6 +28050,8 @@
           <t>NODE_S1974_75_0087</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27956,6 +28066,14 @@
         <is>
           <t>NODE_S1973_74_0093</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -28330,6 +28448,12 @@
           <t>REG_SVM</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0106</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28349,6 +28473,14 @@
         <is>
           <t>NODE_S1973_74_0100</t>
         </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -28612,6 +28744,8 @@
           <t>NODE_S1974_75_0100</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28621,6 +28755,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -28706,6 +28848,8 @@
           <t>NODE_S1974_75_0100</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28715,6 +28859,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -28905,6 +29057,21 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -720,6 +720,11 @@
           <t>SONP Kladno</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -24112,8 +24117,6 @@
           <t>NODE_S1974_75_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24169,8 +24172,6 @@
           <t>NODE_S1974_75_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24936,8 +24937,6 @@
           <t>NODE_S1974_75_0014</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24988,8 +24987,6 @@
           <t>NODE_S1974_75_0014</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25364,8 +25361,6 @@
           <t>NODE_S1974_75_0030</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25599,8 +25594,6 @@
           <t>NODE_S1974_75_0034</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25839,8 +25832,6 @@
           <t>NODE_S1974_75_0034</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26581,8 +26572,6 @@
           <t>NODE_S1974_75_0055</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27511,8 +27500,6 @@
           <t>NODE_S1974_75_0073</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28050,8 +28037,6 @@
           <t>NODE_S1974_75_0087</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28453,7 +28438,6 @@
           <t>NODE_S1974_75_0106</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28744,8 +28728,6 @@
           <t>NODE_S1974_75_0100</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28848,8 +28830,6 @@
           <t>NODE_S1974_75_0100</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29057,21 +29037,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -55075,7 +55040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55303,6 +55268,18 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>Jihlava "B" – Kladno "B" 7:9 zachováno jako významová poznámka sezóny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SONP Kladno</t>
         </is>
       </c>
     </row>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -29037,6 +29037,21 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -37726,6 +37741,7 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
@@ -38277,6 +38293,7 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -41241,6 +41258,7 @@
         </is>
       </c>
     </row>
+    <row r="196"/>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
@@ -43684,6 +43702,7 @@
         </is>
       </c>
     </row>
+    <row r="251"/>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
@@ -43936,6 +43955,7 @@
         </is>
       </c>
     </row>
+    <row r="258"/>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
@@ -45496,6 +45516,7 @@
         </is>
       </c>
     </row>
+    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -49023,6 +49044,7 @@
         </is>
       </c>
     </row>
+    <row r="376"/>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
@@ -51697,6 +51719,7 @@
         </is>
       </c>
     </row>
+    <row r="439"/>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
@@ -53778,6 +53801,7 @@
         </is>
       </c>
     </row>
+    <row r="488"/>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -1656,7 +1656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W44"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4595,6 +4595,476 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Šluknov</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0563</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00474</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ČSAD Chomutov</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0564</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00475</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SSM OVHS Chomutov</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0565</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00476</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ROH VHS Chomutov</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0566</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00477</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Lokomotiva Chomutov</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0567</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00478</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bytový Podnik Chomutov</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0568</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00479</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Baník Kundratice</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0569</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00480</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pěnčín</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0570</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00481</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Železný Brod</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0571</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00482</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Frýdlant</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0572</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00483</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4606,7 +5076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W118"/>
+  <dimension ref="A1:W153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12006,6 +12476,1527 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Sokol Blešno</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0573</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00484</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Slavoj Skřivany</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0574</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00485</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Sokol Skochovice</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0575</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00486</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VŠTJ LF Hradec Králové</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0576</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00487</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sokol Smidary</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0577</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00488</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0578</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00489</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Rosice u Chrasti B</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0579</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00490</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Sokol Jeníšovice B</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0580</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00491</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Sokol Tuněchory</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0581</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00492</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Heřmanův Městec B</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0582</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00493</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Spartak Hedvikov</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0583</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00494</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Sokol Studnice</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0584</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00495</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Slavoj Teplice</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0585</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00496</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Spartak Police</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0586</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00497</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>4</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Sokol Žďárky</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0587</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00498</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>5</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Sokol Bohuslavice</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0588</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00499</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>6</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Rubena Náchod B</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0589</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00500</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VŠCHT Pardubice</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0590</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00501</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Sokol Dolany</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0591</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00502</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Sokol Veselí</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0592</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00503</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sokol Bukovka</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0593</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00504</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0594</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00505</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sokol Častolovice</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0595</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00506</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Sokol Chleny</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0596</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00507</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>4</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Sokol Lupenice</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0597</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00508</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>5</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Sokol Čermná</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0598</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00509</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Potštejn</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0599</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00510</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Doubravice</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0600</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00511</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Rovensko pod Troskami</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0601</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00512</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0602</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00513</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Semanín</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0603</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00514</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Třebovice</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0604</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00515</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>4</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Nekoř</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0605</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00516</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>5</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Králíky</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0606</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00517</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12017,7 +14008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W78"/>
+  <dimension ref="A1:W94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17169,6 +19160,703 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sokol Růžiná</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0607</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00518</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Tatran Bystřice pod Hostýnem</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0608</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00519</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Vodní stavby Kroměříž</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0609</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00520</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sokol Věžky</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0610</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00521</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Sokol Chomýž</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0611</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00522</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0612</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00523</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sokol Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0613</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00524</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sokol Studenec</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0614</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00525</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sokol Želetava</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0615</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00526</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jiskra Vladislav</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0616</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00527</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Družstevník Horní Dunajovice</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0617</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00528</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Slavia Hluboké Mašůvky</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0618</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00529</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Družstevník Oblekovice</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0619</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00530</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TJ Dobšice</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0620</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00531</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>5</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>TJ Pavlice</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0621</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00532</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17180,7 +19868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W58"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -20918,6 +23606,789 @@
       <c r="W58" s="3" t="inlineStr">
         <is>
           <t>finále</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Slovan Orlová</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0622</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00533</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TJ RH OOVB Nový Jičín</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0623</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00534</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Uničovské strojírny</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0624</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00535</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sokol Hnojice</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0625</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00536</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sokol Dlouhá Loučka</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0626</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00537</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sokol Mezice</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0627</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00538</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sokol Šumvald</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0628</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00539</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sokol Štáblovice</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0629</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00540</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sokol Pustkovec</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0630</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00541</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sokol Stará Bělá</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0631</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00542</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RŘ Heřmanice</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0632</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00543</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Josefovice</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0633</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00544</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Tatran Ruda nad Moravou</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0634</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00545</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sokol Postřelmov</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0635</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00546</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Tatran Moravičany</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0636</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00547</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sokol Bohdíkov</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0637</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00548</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sokol Janová</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0638</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00549</t>
         </is>
       </c>
     </row>
@@ -23711,7 +27182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N130"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29143,6 +32614,228 @@
       <c r="K130" t="inlineStr">
         <is>
           <t>Dvouzápasová série Slovan Hodonín – Meochema Přerov 7:3, 2:5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Středočeský – Okresy</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0034</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Jihočeský – Okresy</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>REG_JHC</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0049</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0133</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Severočeský – Okresy</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>REG_SEC</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0066</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0134</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Východočeský – okres Hradec Králové:</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0073</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0135</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Blansko</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0087</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0136</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Severomoravský – Okresy</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0100</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -32909,7 +36602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J521"/>
+  <dimension ref="A1:J644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -55050,6 +58743,3967 @@
       <c r="I521" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0516</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Stavocentrál Kladno</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Stavocentrál Kladno</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0517</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Sokol Žilina</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Sokol Žilina</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0518</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Sokol Řisuty</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Sokol Řisuty</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0519</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Baník Smečno</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Baník Smečno</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0520</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Sokol Jeneč</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Sokol Jeneč</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0521</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Sokol Dobrovíz</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Sokol Dobrovíz</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0522</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0523</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Úder Čáslav</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Úder Čáslav</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0524</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Slavoj Vrdy</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Slavoj Vrdy</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0525</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Sokol Žehušice</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Sokol Žehušice</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0526</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Sokol Bělokozly</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Sokol Bělokozly</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0527</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0528</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0529</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0530</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Slávia PF České Budějovice</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Slávia PF České Budějovice</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0531</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Sokol Římov</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Sokol Římov</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0532</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Byňov</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Byňov</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0533</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Jiskra Týn nad Vltavou</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Jiskra Týn nad Vltavou</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0534</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Sokol Olešník</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Sokol Olešník</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0535</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Sokol Petříkov</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Sokol Petříkov</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0536</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Sokol Ledenice</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Sokol Ledenice</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0537</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Sokol Ševětín</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Sokol Ševětín</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0538</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Slávia VŠZ České Budějovice</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Slávia VŠZ České Budějovice</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0539</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Sokol Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Sokol Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0540</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Spartak Pelhřimov B</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Spartak Pelhřimov B</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0541</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Slavoj Žirovnice</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Slavoj Žirovnice</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0542</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Sokol Bohdalín</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Sokol Bohdalín</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0543</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Tatran Červená Řečice</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Tatran Červená Řečice</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0544</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Sokol Kamenice</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Sokol Kamenice</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0545</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Slavoj Pacov</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Slavoj Pacov</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0546</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Slavoj Želiv</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Slavoj Želiv</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0547</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Sokol Kluky</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Sokol Kluky</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0548</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Sokol Čimelice</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Sokol Čimelice</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0549</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Veselíčko</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Veselíčko</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0550</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Sokol Božetice</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Sokol Božetice</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0551</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Přeborov</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Přeborov</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0552</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Boubská</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Boubská</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0553</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Sokol Cehnice</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Sokol Cehnice</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0554</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Volyně</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Volyně</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0555</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Otavan Štěkeň</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Otavan Štěkeň</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0556</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>JZD Přešťovice</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>JZD Přešťovice</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0557</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Miloňovice</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Miloňovice</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0558</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Sokol Katovice</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Sokol Katovice</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0559</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>JZD Dražice</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>JZD Dražice</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0560</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Sokol Planá nad Lužnicí</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Sokol Planá nad Lužnicí</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0561</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Řepeč</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Řepeč</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0562</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Sokol Želeč</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Sokol Želeč</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0563</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Šluknov</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Šluknov</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0564</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>ČSAD Chomutov</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>ČSAD Chomutov</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0565</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>SSM OVHS Chomutov</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>SSM OVHS Chomutov</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0566</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>ROH VHS Chomutov</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>ROH VHS Chomutov</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0567</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Lokomotiva Chomutov</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Lokomotiva Chomutov</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0568</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Bytový Podnik Chomutov</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Bytový Podnik Chomutov</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0569</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Baník Kundratice</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Baník Kundratice</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0570</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Pěnčín</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Pěnčín</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0571</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Železný Brod</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Železný Brod</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0572</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Frýdlant</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Frýdlant</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0573</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Sokol Blešno</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Sokol Blešno</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0574</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Slavoj Skřivany</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Slavoj Skřivany</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0575</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Sokol Skochovice</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Sokol Skochovice</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0576</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>VŠTJ LF Hradec Králové</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>VŠTJ LF Hradec Králové</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0577</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Sokol Smidary</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Sokol Smidary</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0578</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0579</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Rosice u Chrasti B</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Rosice u Chrasti B</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0580</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Sokol Jeníšovice B</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Sokol Jeníšovice B</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0581</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Sokol Tuněchory</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Sokol Tuněchory</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0582</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Heřmanův Městec B</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Heřmanův Městec B</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0583</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Spartak Hedvikov</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Spartak Hedvikov</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0584</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Sokol Studnice</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Sokol Studnice</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0585</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Slavoj Teplice</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Slavoj Teplice</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0586</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Spartak Police</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Spartak Police</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0587</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Sokol Žďárky</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Sokol Žďárky</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0588</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Sokol Bohuslavice</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Sokol Bohuslavice</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0589</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Rubena Náchod B</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Rubena Náchod B</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0590</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>VŠCHT Pardubice</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>VŠCHT Pardubice</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0591</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Sokol Dolany</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Sokol Dolany</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0592</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Sokol Veselí</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Sokol Veselí</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0593</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Sokol Bukovka</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Sokol Bukovka</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0594</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0595</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Sokol Častolovice</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Sokol Častolovice</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0596</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Sokol Chleny</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Sokol Chleny</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0597</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Sokol Lupenice</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Sokol Lupenice</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0598</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Sokol Čermná</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Sokol Čermná</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0599</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Potštejn</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Potštejn</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0600</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Doubravice</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Doubravice</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0601</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Rovensko pod Troskami</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Rovensko pod Troskami</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0602</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0603</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Semanín</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Semanín</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0604</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Třebovice</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Třebovice</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0605</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Nekoř</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Nekoř</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0606</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Králíky</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Králíky</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0607</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Sokol Růžiná</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Sokol Růžiná</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0608</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Tatran Bystřice pod Hostýnem</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Tatran Bystřice pod Hostýnem</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0609</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Vodní stavby Kroměříž</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Vodní stavby Kroměříž</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0610</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Sokol Věžky</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Sokol Věžky</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0611</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Sokol Chomýž</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Sokol Chomýž</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0612</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0613</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Sokol Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Sokol Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0614</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Sokol Studenec</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Sokol Studenec</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0615</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Sokol Želetava</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Sokol Želetava</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0616</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Jiskra Vladislav</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Jiskra Vladislav</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0617</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Družstevník Horní Dunajovice</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Družstevník Horní Dunajovice</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0618</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Slavia Hluboké Mašůvky</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Slavia Hluboké Mašůvky</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0619</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Družstevník Oblekovice</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Družstevník Oblekovice</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0620</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>TJ Dobšice</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>TJ Dobšice</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0621</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>TJ Pavlice</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>TJ Pavlice</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0622</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Slovan Orlová</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Slovan Orlová</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0623</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>TJ RH OOVB Nový Jičín</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>TJ RH OOVB Nový Jičín</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0624</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Uničovské strojírny</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Uničovské strojírny</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0625</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Sokol Hnojice</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Sokol Hnojice</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0626</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Sokol Dlouhá Loučka</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Sokol Dlouhá Loučka</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0627</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Sokol Mezice</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Sokol Mezice</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0628</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Sokol Šumvald</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Sokol Šumvald</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0629</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Sokol Štáblovice</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Sokol Štáblovice</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0630</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Sokol Pustkovec</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Sokol Pustkovec</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0631</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Sokol Stará Bělá</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Sokol Stará Bělá</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0632</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>RŘ Heřmanice</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>RŘ Heřmanice</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0633</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Josefovice</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Josefovice</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0634</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Tatran Ruda nad Moravou</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Tatran Ruda nad Moravou</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0635</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Sokol Postřelmov</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Sokol Postřelmov</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0636</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Tatran Moravičany</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Tatran Moravičany</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0637</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Sokol Bohdíkov</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Sokol Bohdíkov</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0638</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Sokol Janová</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Sokol Janová</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>
@@ -66656,7 +74310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W88"/>
+  <dimension ref="A1:W103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -72756,6 +80410,631 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Stavocentrál Kladno</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0516</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00427</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sokol Žilina</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0517</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00428</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sokol Řisuty</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0518</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00429</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Baník Smečno</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0519</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00430</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sokol Jeneč</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0520</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00431</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sokol Dobrovíz</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0521</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00432</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0522</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00433</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Úder Čáslav</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0523</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00434</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Slavoj Vrdy</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0524</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00435</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sokol Žehušice</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0525</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00436</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sokol Bělokozly</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0526</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00437</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0527</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00438</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0528</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00439</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0131</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0529</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00440</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -72767,7 +81046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:W95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -76401,6 +84680,1476 @@
       <c r="W61" s="3" t="inlineStr">
         <is>
           <t>1.kolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Slávia PF České Budějovice</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0530</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00441</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sokol Římov</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0531</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00442</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Byňov</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0532</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00443</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jiskra Týn nad Vltavou</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0533</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00444</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sokol Olešník</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0534</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00445</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sokol Petříkov</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0535</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00446</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sokol Ledenice</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0536</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00447</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sokol Ševětín</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0537</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00448</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Slávia VŠZ České Budějovice</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0538</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00449</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sokol Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0539</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00450</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Spartak Pelhřimov B</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0540</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00451</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Slavoj Žirovnice</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0541</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00452</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sokol Bohdalín</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0542</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00453</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Tatran Červená Řečice</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0543</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00454</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Sokol Kamenice</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0544</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00455</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Slavoj Pacov</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0545</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00456</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Slavoj Želiv</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0546</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00457</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sokol Kluky</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0547</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00458</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Sokol Čimelice</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0548</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00459</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Veselíčko</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0549</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00460</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sokol Božetice</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0550</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00461</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Přeborov</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0551</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00462</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Boubská</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0552</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00463</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sokol Cehnice</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0553</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00464</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Volyně</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0554</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00465</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Otavan Štěkeň</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0555</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00466</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>JZD Přešťovice</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0556</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00467</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Miloňovice</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0557</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00468</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>7</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sokol Katovice</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0558</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00469</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>JZD Dražice</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0559</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00470</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sokol Planá nad Lužnicí</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0560</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00471</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Řepeč</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0561</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00472</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sokol Želeč</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Okresy</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0132</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>CLUB_S1974_75_0562</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>TR_S1974_75_00473</t>
         </is>
       </c>
     </row>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +91,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -100,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,6 +121,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -32508,21 +32519,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -41434,7 +41430,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
@@ -41986,7 +41981,6 @@
         </is>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -44951,7 +44945,6 @@
         </is>
       </c>
     </row>
-    <row r="196"/>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
@@ -47395,7 +47388,6 @@
         </is>
       </c>
     </row>
-    <row r="251"/>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
@@ -47648,7 +47640,6 @@
         </is>
       </c>
     </row>
-    <row r="258"/>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
@@ -49209,7 +49200,6 @@
         </is>
       </c>
     </row>
-    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -52737,7 +52727,6 @@
         </is>
       </c>
     </row>
-    <row r="376"/>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
@@ -55412,7 +55401,6 @@
         </is>
       </c>
     </row>
-    <row r="439"/>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
@@ -57494,7 +57482,6 @@
         </is>
       </c>
     </row>
-    <row r="488"/>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
@@ -62972,7 +62959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -63029,7 +63016,7 @@
           <t>CLUB_S1974_75_0015</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63049,7 +63036,7 @@
           <t>CLUB_S1974_75_0031</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63069,7 +63056,7 @@
           <t>CLUB_S1974_75_0040</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63089,7 +63076,7 @@
           <t>CLUB_S1974_75_0050</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -63109,7 +63096,7 @@
           <t>CLUB_S1974_75_0052</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63129,7 +63116,7 @@
           <t>CLUB_S1974_75_0056</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63149,7 +63136,7 @@
           <t>CLUB_S1974_75_0059</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
@@ -63169,7 +63156,7 @@
           <t>CLUB_S1974_75_0062</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63189,7 +63176,7 @@
           <t>CLUB_S1974_75_0064</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -63209,7 +63196,7 @@
           <t>CLUB_S1974_75_0066</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -63229,7 +63216,7 @@
           <t>CLUB_S1974_75_0078</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -63249,7 +63236,7 @@
           <t>CLUB_S1974_75_0086</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63269,7 +63256,7 @@
           <t>CLUB_S1974_75_0108</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63289,7 +63276,7 @@
           <t>CLUB_S1974_75_0515</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Technické Služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63309,7 +63296,7 @@
           <t>CLUB_S1974_75_0199</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63329,7 +63316,7 @@
           <t>CLUB_S1974_75_0213</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63349,7 +63336,7 @@
           <t>CLUB_S1974_75_0232</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
@@ -63369,7 +63356,7 @@
           <t>CLUB_S1974_75_0309</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63389,7 +63376,7 @@
           <t>CLUB_S1974_75_0378</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1973_74_0458 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -63409,7 +63396,7 @@
           <t>CLUB_S1974_75_0399</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63429,7 +63416,7 @@
           <t>CLUB_S1974_75_0414</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -63449,7 +63436,7 @@
           <t>CLUB_S1974_75_0420</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63469,7 +63456,7 @@
           <t>CLUB_S1974_75_0425</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63489,7 +63476,7 @@
           <t>CLUB_S1974_75_0447</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -63509,7 +63496,7 @@
           <t>CLUB_S1974_75_0491</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63529,7 +63516,7 @@
           <t>CLUB_S1974_75_0494</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63549,7 +63536,7 @@
           <t>CLUB_S1974_75_0496</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -63569,7 +63556,7 @@
           <t>CLUB_S1974_75_0128</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
@@ -63589,7 +63576,7 @@
           <t>CLUB_S1974_75_0196</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
@@ -63609,7 +63596,7 @@
           <t>CLUB_S1974_75_0251</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
@@ -63629,7 +63616,7 @@
           <t>CLUB_S1974_75_0258</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
@@ -63649,7 +63636,7 @@
           <t>CLUB_S1974_75_0294</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
@@ -63669,7 +63656,7 @@
           <t>CLUB_S1974_75_0376</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
@@ -63689,7 +63676,7 @@
           <t>CLUB_S1974_75_0439</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
@@ -63709,11 +63696,115 @@
           <t>CLUB_S1974_75_0488</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>30_Západočeský L50 skupina A (západní Čechy) · NODE_S1974_75_0057</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (TJ Sokol Losiná), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>30_Západočeský L50 skupina B (západní Čechy) · NODE_S1974_75_0058</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (TJ Vlna Nejdek, SK Mariánské Lázně), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>30_Západočeský L50 finále (západní Čechy) · NODE_S1974_75_0059</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (TJ Vlna Nejdek -), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>30_Západočeský L50 skupina C (západní Čechy) · NODE_S1974_75_0063</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (Tatran Luby, Klatovy), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F36"/>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,6 +123,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -26698,7 +26701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27177,6 +27180,74 @@
         </is>
       </c>
       <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0057</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (TJ Sokol Losiná), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0058</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (TJ Vlna Nejdek, SK Mariánské Lázně), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0059</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (TJ Vlna Nejdek -), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0063</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (Tatran Luby, Klatovy), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -63716,7 +63787,7 @@
           <t>30_Západočeský L50 skupina A (západní Čechy) · NODE_S1974_75_0057</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (TJ Sokol Losiná), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -63742,7 +63813,7 @@
           <t>30_Západočeský L50 skupina B (západní Čechy) · NODE_S1974_75_0058</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (TJ Vlna Nejdek, SK Mariánské Lázně), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -63768,7 +63839,7 @@
           <t>30_Západočeský L50 finále (západní Čechy) · NODE_S1974_75_0059</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (TJ Vlna Nejdek -), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -63794,7 +63865,7 @@
           <t>30_Západočeský L50 skupina C (západní Čechy) · NODE_S1974_75_0063</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (Tatran Luby, Klatovy), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -28363,7 +28363,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Divize SVK Západ</t>
+          <t>Divize Slovensko Západ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -28415,7 +28415,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Divize SVK Východ</t>
+          <t>Divize Slovensko Východ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Divize SVK finále</t>
+          <t>Divize Slovensko finále</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Divize SVK o udržení</t>
+          <t>Divize Slovensko o udržení</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -28666,7 +28666,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Praha L60</t>
+          <t>Praha, 6. úroveň</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L60</t>
+          <t>Praha, 6. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Praha L60 skupina A</t>
+          <t>Praha, 6. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -28844,7 +28844,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L60 skupina B</t>
+          <t>Praha, 6. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -28891,7 +28891,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L60 finále</t>
+          <t>Praha, 6. úroveň, finále</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -28993,7 +28993,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Středočeský L60</t>
+          <t>Středočeský, 6. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina A</t>
+          <t>Středočeský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -29082,7 +29082,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina B</t>
+          <t>Středočeský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -29124,7 +29124,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 finále</t>
+          <t>Středočeský, 5. úroveň, finále</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -29174,7 +29174,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 I.A třída</t>
+          <t>Středočeský, 5. úroveň I.A třída</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -29221,7 +29221,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina A</t>
+          <t>Středočeský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina B</t>
+          <t>Středočeský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -29315,7 +29315,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina C</t>
+          <t>Středočeský, 5. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 finále</t>
+          <t>Středočeský, 5. úroveň, finále</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -29412,7 +29412,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 I.B třída</t>
+          <t>Středočeský, 5. úroveň I.B třída</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina A</t>
+          <t>Středočeský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -29506,7 +29506,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina B</t>
+          <t>Středočeský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -29553,7 +29553,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina C</t>
+          <t>Středočeský, 5. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Středočeský L50 skupina D</t>
+          <t>Středočeský, 5. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -29647,7 +29647,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Jihočeský L60</t>
+          <t>Jihočeský, 6. úroveň</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -29741,7 +29741,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50 II.třída</t>
+          <t>Jihočeský, 5. úroveň II.třída</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -29783,7 +29783,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50 skupina A</t>
+          <t>Jihočeský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -29825,7 +29825,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50 skupina B</t>
+          <t>Jihočeský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Jihočeský Kvalifikace o KP II</t>
+          <t>Jihočeský Kvalifikace o KP II</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -29961,7 +29961,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Západočeský L60</t>
+          <t>Západočeský, 6. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -30008,7 +30008,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Západočeský L50 skupina A</t>
+          <t>Západočeský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -30055,7 +30055,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Západočeský L50 skupina B</t>
+          <t>Západočeský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -30102,7 +30102,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Západočeský L50 finále</t>
+          <t>Západočeský, 5. úroveň, finále</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -30157,7 +30157,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Západočeský L50 II.třída</t>
+          <t>Západočeský, 5. úroveň II.třída</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -30199,7 +30199,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Západočeský L50 skupina A</t>
+          <t>Západočeský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -30246,7 +30246,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Západočeský L50 skupina B</t>
+          <t>Západočeský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -30293,7 +30293,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Západočeský L50 skupina C</t>
+          <t>Západočeský, 5. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -30340,7 +30340,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Západočeský kvalifikace</t>
+          <t>Západočeský kvalifikace</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -30392,7 +30392,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Západočeský kvalifikace o I.třídu</t>
+          <t>Západočeský kvalifikace o I.třídu</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -30491,7 +30491,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Severočeský L60</t>
+          <t>Severočeský, 6. úroveň</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Severočeský L50 I.třída</t>
+          <t>Severočeský, 5. úroveň I.třída</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Severočeský L50 skupina A</t>
+          <t>Severočeský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -30632,7 +30632,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Severočeský L50 skupina B</t>
+          <t>Severočeský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Severočeský L50 skupina C</t>
+          <t>Severočeský, 5. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Severočeský Kvalifikace</t>
+          <t>Severočeský Kvalifikace</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -30773,7 +30773,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Východočeský L60</t>
+          <t>Východočeský, 6. úroveň</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 skupina A-pohárová část</t>
+          <t>Východočeský, 5. úroveň, skupina A-pohárová část</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -30904,7 +30904,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 skupina A-konečná tabulka</t>
+          <t>Východočeský, 5. úroveň, skupina A-konečná tabulka</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -30946,7 +30946,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 skupina B-pohárová část</t>
+          <t>Východočeský, 5. úroveň, skupina B-pohárová část</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 skupina B-konečná tabulka</t>
+          <t>Východočeský, 5. úroveň, skupina B-konečná tabulka</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -31030,7 +31030,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 finále</t>
+          <t>Východočeský, 5. úroveň, finále</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Východočeský L60 skupina A</t>
+          <t>Východočeský, 6. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -31122,7 +31122,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Východočeský L60 skupina B</t>
+          <t>Východočeský, 6. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Východočeský L60 skupina C</t>
+          <t>Východočeský, 6. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Východočeský L60 skupina D</t>
+          <t>Východočeský, 6. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Východočeský L60 skupina E</t>
+          <t>Východočeský, 6. úroveň, skupina E</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Východočeský kvalifikace o krajský přebor</t>
+          <t>Východočeský kvalifikace o krajský přebor</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Východočeský kvalifikace</t>
+          <t>Východočeský kvalifikace</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -31384,7 +31384,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -31431,7 +31431,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L60</t>
+          <t>Jihomoravský, 6. úroveň</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -31473,7 +31473,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 skupina A</t>
+          <t>Jihomoravský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -31520,7 +31520,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 skupina B</t>
+          <t>Jihomoravský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -31567,7 +31567,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 finále</t>
+          <t>Jihomoravský, 5. úroveň, finále</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -31622,7 +31622,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 II.třída</t>
+          <t>Jihomoravský, 5. úroveň II.třída</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -31664,7 +31664,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 skupina A</t>
+          <t>Jihomoravský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -31706,7 +31706,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 skupina B</t>
+          <t>Jihomoravský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -31748,7 +31748,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 skupina C</t>
+          <t>Jihomoravský, 5. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -31790,7 +31790,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 skupina D</t>
+          <t>Jihomoravský, 5. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -31832,7 +31832,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50 skupina E</t>
+          <t>Jihomoravský, 5. úroveň, skupina E</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30_Jihomoravský kvalifikace</t>
+          <t>Jihomoravský kvalifikace</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -31921,7 +31921,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30_Jihomoravský Kvalifikace</t>
+          <t>Jihomoravský Kvalifikace</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -32028,7 +32028,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>30_Severomoravský L60</t>
+          <t>Severomoravský, 6. úroveň</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -32075,7 +32075,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50 KP II.třídy</t>
+          <t>Severomoravský, 5. úroveň KP II.třídy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50 skupina A</t>
+          <t>Severomoravský, 5. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -32164,7 +32164,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50 skupina B</t>
+          <t>Severomoravský, 5. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -32211,7 +32211,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50 skupina C</t>
+          <t>Severomoravský, 5. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -32258,7 +32258,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50 finále</t>
+          <t>Severomoravský, 5. úroveň, finále</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -32308,7 +32308,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>30_Severomoravský Kvalifikace o I.třídu</t>
+          <t>Severomoravský Kvalifikace o I.třídu</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50 finále</t>
+          <t>Severomoravský, 5. úroveň, finále</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -32410,7 +32410,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>30_SVK L50</t>
+          <t>Slovensko, 5. úroveň</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -32457,7 +32457,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30_SVK L50 Západoslovenský krajský přebor</t>
+          <t>Slovensko, 5. úroveň Západoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -32504,7 +32504,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>30_SVK L50 Středoslovenský krajský přebor</t>
+          <t>Slovensko, 5. úroveň Středoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -32551,7 +32551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>30_SVK L50 Východoslovenský krajský přebor</t>
+          <t>Slovensko, 5. úroveň Východoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -32590,6 +32590,21 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>

--- a/data/S1974_75_FINAL.xlsx
+++ b/data/S1974_75_FINAL.xlsx
@@ -32590,21 +32590,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -64196,7 +64181,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>kvalifikace</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -66406,7 +66391,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -71408,7 +71393,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -71491,7 +71476,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -71725,7 +71710,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
